--- a/utils/Intermediates/250121_Gschool_moe_mosdot_coordinates_2022.xlsx
+++ b/utils/Intermediates/250121_Gschool_moe_mosdot_coordinates_2022.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F520"/>
+  <dimension ref="A1:G520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>coordinate_y</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SRC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -485,6 +490,11 @@
       <c r="F2" t="n">
         <v>634787</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -511,6 +521,11 @@
       <c r="F3" t="n">
         <v>634711</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -537,6 +552,11 @@
       <c r="F4" t="n">
         <v>630138</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -563,6 +583,11 @@
       <c r="F5" t="n">
         <v>631692</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -589,6 +614,11 @@
       <c r="F6" t="n">
         <v>604302</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -615,6 +645,11 @@
       <c r="F7" t="n">
         <v>618361</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -641,6 +676,11 @@
       <c r="F8" t="n">
         <v>634300</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -667,6 +707,11 @@
       <c r="F9" t="n">
         <v>619667</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -693,6 +738,11 @@
       <c r="F10" t="n">
         <v>604155</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -719,6 +769,11 @@
       <c r="F11" t="n">
         <v>651635</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -745,6 +800,11 @@
       <c r="F12" t="n">
         <v>631931</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -771,6 +831,11 @@
       <c r="F13" t="n">
         <v>642482</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -797,6 +862,11 @@
       <c r="F14" t="n">
         <v>649776</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -823,6 +893,11 @@
       <c r="F15" t="n">
         <v>656868</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -849,6 +924,11 @@
       <c r="F16" t="n">
         <v>635674</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -875,6 +955,11 @@
       <c r="F17" t="n">
         <v>637205</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -901,6 +986,11 @@
       <c r="F18" t="n">
         <v>660155</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -927,6 +1017,11 @@
       <c r="F19" t="n">
         <v>622275</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -953,6 +1048,11 @@
       <c r="F20" t="n">
         <v>645348</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -979,6 +1079,11 @@
       <c r="F21" t="n">
         <v>662197</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1005,6 +1110,11 @@
       <c r="F22" t="n">
         <v>635725</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1031,6 +1141,11 @@
       <c r="F23" t="n">
         <v>631282</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1057,6 +1172,11 @@
       <c r="F24" t="n">
         <v>652271</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1083,6 +1203,11 @@
       <c r="F25" t="n">
         <v>611662</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1109,6 +1234,11 @@
       <c r="F26" t="n">
         <v>618198</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1135,6 +1265,11 @@
       <c r="F27" t="n">
         <v>634337</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1161,6 +1296,11 @@
       <c r="F28" t="n">
         <v>634631</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1187,6 +1327,11 @@
       <c r="F29" t="n">
         <v>628899</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1213,6 +1358,11 @@
       <c r="F30" t="n">
         <v>641077</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1239,6 +1389,11 @@
       <c r="F31" t="n">
         <v>639890</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1265,6 +1420,11 @@
       <c r="F32" t="n">
         <v>667545</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1291,6 +1451,11 @@
       <c r="F33" t="n">
         <v>617664</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1317,6 +1482,11 @@
       <c r="F34" t="n">
         <v>634418</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1343,6 +1513,11 @@
       <c r="F35" t="n">
         <v>648580</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1369,6 +1544,11 @@
       <c r="F36" t="n">
         <v>637176</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1395,6 +1575,11 @@
       <c r="F37" t="n">
         <v>622723</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1421,6 +1606,11 @@
       <c r="F38" t="n">
         <v>633376</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1447,6 +1637,11 @@
       <c r="F39" t="n">
         <v>604174</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1473,6 +1668,11 @@
       <c r="F40" t="n">
         <v>631486</v>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1499,6 +1699,11 @@
       <c r="F41" t="n">
         <v>631554</v>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1525,6 +1730,11 @@
       <c r="F42" t="n">
         <v>649843</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1551,6 +1761,11 @@
       <c r="F43" t="n">
         <v>648536</v>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1577,6 +1792,11 @@
       <c r="F44" t="n">
         <v>651894</v>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1603,6 +1823,11 @@
       <c r="F45" t="n">
         <v>622572</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1629,6 +1854,11 @@
       <c r="F46" t="n">
         <v>651715</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1655,6 +1885,11 @@
       <c r="F47" t="n">
         <v>648880</v>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1681,6 +1916,11 @@
       <c r="F48" t="n">
         <v>630586</v>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1707,6 +1947,11 @@
       <c r="F49" t="n">
         <v>643124</v>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1733,6 +1978,11 @@
       <c r="F50" t="n">
         <v>640938</v>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1759,6 +2009,11 @@
       <c r="F51" t="n">
         <v>630850</v>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1785,6 +2040,11 @@
       <c r="F52" t="n">
         <v>622276</v>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1811,6 +2071,11 @@
       <c r="F53" t="n">
         <v>604302</v>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1837,6 +2102,11 @@
       <c r="F54" t="n">
         <v>620908</v>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1863,6 +2133,11 @@
       <c r="F55" t="n">
         <v>648059</v>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1889,6 +2164,11 @@
       <c r="F56" t="n">
         <v>622445</v>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1915,6 +2195,11 @@
       <c r="F57" t="n">
         <v>619164</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1941,6 +2226,11 @@
       <c r="F58" t="n">
         <v>630990</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1967,6 +2257,11 @@
       <c r="F59" t="n">
         <v>634877</v>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1993,6 +2288,11 @@
       <c r="F60" t="n">
         <v>619657</v>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2019,6 +2319,11 @@
       <c r="F61" t="n">
         <v>622503</v>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2045,6 +2350,11 @@
       <c r="F62" t="n">
         <v>648699</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2071,6 +2381,11 @@
       <c r="F63" t="n">
         <v>648709</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2097,6 +2412,11 @@
       <c r="F64" t="n">
         <v>645977</v>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2123,6 +2443,11 @@
       <c r="F65" t="n">
         <v>644699</v>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2149,6 +2474,11 @@
       <c r="F66" t="n">
         <v>645735</v>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2175,6 +2505,11 @@
       <c r="F67" t="n">
         <v>644818</v>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2201,6 +2536,11 @@
       <c r="F68" t="n">
         <v>645100</v>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2227,6 +2567,11 @@
       <c r="F69" t="n">
         <v>635375</v>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2253,6 +2598,11 @@
       <c r="F70" t="n">
         <v>633685</v>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2279,6 +2629,11 @@
       <c r="F71" t="n">
         <v>631804</v>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2305,6 +2660,11 @@
       <c r="F72" t="n">
         <v>635086</v>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2331,6 +2691,11 @@
       <c r="F73" t="n">
         <v>635459</v>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2357,6 +2722,11 @@
       <c r="F74" t="n">
         <v>636004</v>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2383,6 +2753,11 @@
       <c r="F75" t="n">
         <v>622940</v>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2409,6 +2784,11 @@
       <c r="F76" t="n">
         <v>648935</v>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2435,6 +2815,11 @@
       <c r="F77" t="n">
         <v>623114</v>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2461,6 +2846,11 @@
       <c r="F78" t="n">
         <v>622924</v>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2487,6 +2877,11 @@
       <c r="F79" t="n">
         <v>631582</v>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2513,6 +2908,11 @@
       <c r="F80" t="n">
         <v>648567</v>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2539,6 +2939,11 @@
       <c r="F81" t="n">
         <v>634382</v>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2565,6 +2970,11 @@
       <c r="F82" t="n">
         <v>648540</v>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2591,6 +3001,11 @@
       <c r="F83" t="n">
         <v>605607</v>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2617,6 +3032,11 @@
       <c r="F84" t="n">
         <v>622415</v>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2643,6 +3063,11 @@
       <c r="F85" t="n">
         <v>618505</v>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2669,6 +3094,11 @@
       <c r="F86" t="n">
         <v>646368</v>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2695,6 +3125,11 @@
       <c r="F87" t="n">
         <v>646279</v>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2721,6 +3156,11 @@
       <c r="F88" t="n">
         <v>622365</v>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2747,6 +3187,11 @@
       <c r="F89" t="n">
         <v>648451</v>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2773,6 +3218,11 @@
       <c r="F90" t="n">
         <v>624769</v>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2799,6 +3249,11 @@
       <c r="F91" t="n">
         <v>648952</v>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2825,6 +3280,11 @@
       <c r="F92" t="n">
         <v>634156</v>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2851,6 +3311,11 @@
       <c r="F93" t="n">
         <v>603876</v>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2877,6 +3342,11 @@
       <c r="F94" t="n">
         <v>617786</v>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2903,6 +3373,11 @@
       <c r="F95" t="n">
         <v>634209</v>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2929,6 +3404,11 @@
       <c r="F96" t="n">
         <v>630930</v>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2955,6 +3435,11 @@
       <c r="F97" t="n">
         <v>605664</v>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2981,6 +3466,11 @@
       <c r="F98" t="n">
         <v>618320</v>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3007,6 +3497,11 @@
       <c r="F99" t="n">
         <v>649424</v>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3033,6 +3528,11 @@
       <c r="F100" t="n">
         <v>648448</v>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3059,6 +3559,11 @@
       <c r="F101" t="n">
         <v>651571</v>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3085,6 +3590,11 @@
       <c r="F102" t="n">
         <v>641245</v>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3111,6 +3621,11 @@
       <c r="F103" t="n">
         <v>617382</v>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3137,6 +3652,11 @@
       <c r="F104" t="n">
         <v>635611</v>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3163,6 +3683,11 @@
       <c r="F105" t="n">
         <v>631535</v>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3189,6 +3714,11 @@
       <c r="F106" t="n">
         <v>651576</v>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3215,6 +3745,11 @@
       <c r="F107" t="n">
         <v>599439</v>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3241,6 +3776,11 @@
       <c r="F108" t="n">
         <v>648675</v>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3267,6 +3807,11 @@
       <c r="F109" t="n">
         <v>648317</v>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3293,6 +3838,11 @@
       <c r="F110" t="n">
         <v>650379</v>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3319,6 +3869,11 @@
       <c r="F111" t="n">
         <v>662267</v>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3345,6 +3900,11 @@
       <c r="F112" t="n">
         <v>619737</v>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3371,6 +3931,11 @@
       <c r="F113" t="n">
         <v>622085</v>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3397,6 +3962,11 @@
       <c r="F114" t="n">
         <v>589009</v>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3423,6 +3993,11 @@
       <c r="F115" t="n">
         <v>656126</v>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3449,6 +4024,11 @@
       <c r="F116" t="n">
         <v>644436</v>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3475,6 +4055,11 @@
       <c r="F117" t="n">
         <v>610418</v>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3501,6 +4086,11 @@
       <c r="F118" t="n">
         <v>664381</v>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3527,6 +4117,11 @@
       <c r="F119" t="n">
         <v>662197</v>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3553,6 +4148,11 @@
       <c r="F120" t="n">
         <v>623119</v>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3579,6 +4179,11 @@
       <c r="F121" t="n">
         <v>605761</v>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3605,6 +4210,11 @@
       <c r="F122" t="n">
         <v>643915</v>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3631,6 +4241,11 @@
       <c r="F123" t="n">
         <v>650180</v>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3657,6 +4272,11 @@
       <c r="F124" t="n">
         <v>634440</v>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3683,6 +4303,11 @@
       <c r="F125" t="n">
         <v>633126</v>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3709,6 +4334,11 @@
       <c r="F126" t="n">
         <v>633447</v>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3735,6 +4365,11 @@
       <c r="F127" t="n">
         <v>645117</v>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3761,6 +4396,11 @@
       <c r="F128" t="n">
         <v>646131</v>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3787,6 +4427,11 @@
       <c r="F129" t="n">
         <v>644222</v>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3813,6 +4458,11 @@
       <c r="F130" t="n">
         <v>646477</v>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3839,6 +4489,11 @@
       <c r="F131" t="n">
         <v>648720</v>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3865,6 +4520,11 @@
       <c r="F132" t="n">
         <v>635378</v>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3891,6 +4551,11 @@
       <c r="F133" t="n">
         <v>622538</v>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3917,6 +4582,11 @@
       <c r="F134" t="n">
         <v>648452</v>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3943,6 +4613,11 @@
       <c r="F135" t="n">
         <v>649035</v>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3969,6 +4644,11 @@
       <c r="F136" t="n">
         <v>647923</v>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3995,6 +4675,11 @@
       <c r="F137" t="n">
         <v>639761</v>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4021,6 +4706,11 @@
       <c r="F138" t="n">
         <v>631971</v>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4047,6 +4737,11 @@
       <c r="F139" t="n">
         <v>631573</v>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4073,6 +4768,11 @@
       <c r="F140" t="n">
         <v>632146</v>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4099,6 +4799,11 @@
       <c r="F141" t="n">
         <v>619419</v>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4125,6 +4830,11 @@
       <c r="F142" t="n">
         <v>644187</v>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4151,6 +4861,11 @@
       <c r="F143" t="n">
         <v>623552</v>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4177,6 +4892,11 @@
       <c r="F144" t="n">
         <v>622542</v>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4203,6 +4923,11 @@
       <c r="F145" t="n">
         <v>622747</v>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4229,6 +4954,11 @@
       <c r="F146" t="n">
         <v>649484</v>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4255,6 +4985,11 @@
       <c r="F147" t="n">
         <v>643718</v>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4281,6 +5016,11 @@
       <c r="F148" t="n">
         <v>642790</v>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4307,6 +5047,11 @@
       <c r="F149" t="n">
         <v>664238</v>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4333,6 +5078,11 @@
       <c r="F150" t="n">
         <v>620776</v>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4359,6 +5109,11 @@
       <c r="F151" t="n">
         <v>603936</v>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4385,6 +5140,11 @@
       <c r="F152" t="n">
         <v>631712</v>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -4411,6 +5171,11 @@
       <c r="F153" t="n">
         <v>646898</v>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4437,6 +5202,11 @@
       <c r="F154" t="n">
         <v>645736</v>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4463,6 +5233,11 @@
       <c r="F155" t="n">
         <v>646683</v>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4489,6 +5264,11 @@
       <c r="F156" t="n">
         <v>645361</v>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4515,6 +5295,11 @@
       <c r="F157" t="n">
         <v>650894</v>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4541,6 +5326,11 @@
       <c r="F158" t="n">
         <v>641776</v>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4567,6 +5357,11 @@
       <c r="F159" t="n">
         <v>647463</v>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4593,6 +5388,11 @@
       <c r="F160" t="n">
         <v>622780</v>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4619,6 +5419,11 @@
       <c r="F161" t="n">
         <v>631689</v>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4645,6 +5450,11 @@
       <c r="F162" t="n">
         <v>630259</v>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4671,6 +5481,11 @@
       <c r="F163" t="n">
         <v>623269</v>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4697,6 +5512,11 @@
       <c r="F164" t="n">
         <v>648999</v>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4723,6 +5543,11 @@
       <c r="F165" t="n">
         <v>648437</v>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4749,6 +5574,11 @@
       <c r="F166" t="n">
         <v>618564</v>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4775,6 +5605,11 @@
       <c r="F167" t="n">
         <v>650778</v>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4801,6 +5636,11 @@
       <c r="F168" t="n">
         <v>642798</v>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4827,6 +5667,11 @@
       <c r="F169" t="n">
         <v>646193</v>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4853,6 +5698,11 @@
       <c r="F170" t="n">
         <v>622258</v>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4879,6 +5729,11 @@
       <c r="F171" t="n">
         <v>647973</v>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4905,6 +5760,11 @@
       <c r="F172" t="n">
         <v>649416</v>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4931,6 +5791,11 @@
       <c r="F173" t="n">
         <v>646736</v>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4957,6 +5822,11 @@
       <c r="F174" t="n">
         <v>620363</v>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4983,6 +5853,11 @@
       <c r="F175" t="n">
         <v>649369</v>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5009,6 +5884,11 @@
       <c r="F176" t="n">
         <v>648597</v>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5035,6 +5915,11 @@
       <c r="F177" t="n">
         <v>623443</v>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5061,6 +5946,11 @@
       <c r="F178" t="n">
         <v>648059</v>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5087,6 +5977,11 @@
       <c r="F179" t="n">
         <v>649589</v>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5113,6 +6008,11 @@
       <c r="F180" t="n">
         <v>622420</v>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5139,6 +6039,11 @@
       <c r="F181" t="n">
         <v>642941</v>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5165,6 +6070,11 @@
       <c r="F182" t="n">
         <v>642788</v>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -5191,6 +6101,11 @@
       <c r="F183" t="n">
         <v>643232</v>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -5217,6 +6132,11 @@
       <c r="F184" t="n">
         <v>623262</v>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5243,6 +6163,11 @@
       <c r="F185" t="n">
         <v>634480</v>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -5269,6 +6194,11 @@
       <c r="F186" t="n">
         <v>623034</v>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -5295,6 +6225,11 @@
       <c r="F187" t="n">
         <v>646123</v>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -5321,6 +6256,11 @@
       <c r="F188" t="n">
         <v>643479</v>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -5347,6 +6287,11 @@
       <c r="F189" t="n">
         <v>643128</v>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -5373,6 +6318,11 @@
       <c r="F190" t="n">
         <v>649670</v>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -5399,6 +6349,11 @@
       <c r="F191" t="n">
         <v>649101</v>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5425,6 +6380,11 @@
       <c r="F192" t="n">
         <v>646871</v>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -5451,6 +6411,11 @@
       <c r="F193" t="n">
         <v>623565</v>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -5477,6 +6442,11 @@
       <c r="F194" t="n">
         <v>643105</v>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5503,6 +6473,11 @@
       <c r="F195" t="n">
         <v>623026</v>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5529,6 +6504,11 @@
       <c r="F196" t="n">
         <v>664219</v>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5555,6 +6535,11 @@
       <c r="F197" t="n">
         <v>643273</v>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5581,6 +6566,11 @@
       <c r="F198" t="n">
         <v>632719</v>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -5607,6 +6597,11 @@
       <c r="F199" t="n">
         <v>646296</v>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5633,6 +6628,11 @@
       <c r="F200" t="n">
         <v>631918</v>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -5659,6 +6659,11 @@
       <c r="F201" t="n">
         <v>646944</v>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -5685,6 +6690,11 @@
       <c r="F202" t="n">
         <v>634887</v>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5711,6 +6721,11 @@
       <c r="F203" t="n">
         <v>650074</v>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5737,6 +6752,11 @@
       <c r="F204" t="n">
         <v>623164</v>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5763,6 +6783,11 @@
       <c r="F205" t="n">
         <v>634247</v>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5789,6 +6814,11 @@
       <c r="F206" t="n">
         <v>648992</v>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5815,6 +6845,11 @@
       <c r="F207" t="n">
         <v>623053</v>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5841,6 +6876,11 @@
       <c r="F208" t="n">
         <v>623481</v>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5867,6 +6907,11 @@
       <c r="F209" t="n">
         <v>623134</v>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5893,6 +6938,11 @@
       <c r="F210" t="n">
         <v>648354</v>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5919,6 +6969,11 @@
       <c r="F211" t="n">
         <v>622689</v>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5945,6 +7000,11 @@
       <c r="F212" t="n">
         <v>622730</v>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5971,6 +7031,11 @@
       <c r="F213" t="n">
         <v>649869</v>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5997,6 +7062,11 @@
       <c r="F214" t="n">
         <v>648621</v>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -6023,6 +7093,11 @@
       <c r="F215" t="n">
         <v>667335</v>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -6049,6 +7124,11 @@
       <c r="F216" t="n">
         <v>660506</v>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -6075,6 +7155,11 @@
       <c r="F217" t="n">
         <v>623080</v>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -6101,6 +7186,11 @@
       <c r="F218" t="n">
         <v>648619</v>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -6127,6 +7217,11 @@
       <c r="F219" t="n">
         <v>631573</v>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -6153,6 +7248,11 @@
       <c r="F220" t="n">
         <v>632430</v>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -6179,6 +7279,11 @@
       <c r="F221" t="n">
         <v>647902</v>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -6205,6 +7310,11 @@
       <c r="F222" t="n">
         <v>648993</v>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -6231,6 +7341,11 @@
       <c r="F223" t="n">
         <v>649729</v>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -6257,6 +7372,11 @@
       <c r="F224" t="n">
         <v>622928</v>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -6283,6 +7403,11 @@
       <c r="F225" t="n">
         <v>649625</v>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -6309,6 +7434,11 @@
       <c r="F226" t="n">
         <v>649737</v>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -6335,6 +7465,11 @@
       <c r="F227" t="n">
         <v>647306</v>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -6361,6 +7496,11 @@
       <c r="F228" t="n">
         <v>648531</v>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -6387,6 +7527,11 @@
       <c r="F229" t="n">
         <v>628709</v>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -6413,6 +7558,11 @@
       <c r="F230" t="n">
         <v>651778</v>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6439,6 +7589,11 @@
       <c r="F231" t="n">
         <v>645211</v>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6465,6 +7620,11 @@
       <c r="F232" t="n">
         <v>642915</v>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6491,6 +7651,11 @@
       <c r="F233" t="n">
         <v>639810</v>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6517,6 +7682,11 @@
       <c r="F234" t="n">
         <v>646736</v>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -6543,6 +7713,11 @@
       <c r="F235" t="n">
         <v>634358</v>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -6569,6 +7744,11 @@
       <c r="F236" t="n">
         <v>623043</v>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -6595,6 +7775,11 @@
       <c r="F237" t="n">
         <v>622453</v>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -6621,6 +7806,11 @@
       <c r="F238" t="n">
         <v>649679</v>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -6647,6 +7837,11 @@
       <c r="F239" t="n">
         <v>645863</v>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -6673,6 +7868,11 @@
       <c r="F240" t="n">
         <v>649737</v>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -6699,6 +7899,11 @@
       <c r="F241" t="n">
         <v>622514</v>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6725,6 +7930,11 @@
       <c r="F242" t="n">
         <v>623445</v>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -6751,6 +7961,11 @@
       <c r="F243" t="n">
         <v>647405</v>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -6777,6 +7992,11 @@
       <c r="F244" t="n">
         <v>648698</v>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -6803,6 +8023,11 @@
       <c r="F245" t="n">
         <v>633382</v>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -6829,6 +8054,11 @@
       <c r="F246" t="n">
         <v>649020</v>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -6855,6 +8085,11 @@
       <c r="F247" t="n">
         <v>648951</v>
       </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -6881,6 +8116,11 @@
       <c r="F248" t="n">
         <v>624615</v>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6907,6 +8147,11 @@
       <c r="F249" t="n">
         <v>649174</v>
       </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6933,6 +8178,11 @@
       <c r="F250" t="n">
         <v>648355</v>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6959,6 +8209,11 @@
       <c r="F251" t="n">
         <v>622259</v>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6985,6 +8240,11 @@
       <c r="F252" t="n">
         <v>648836</v>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -7011,6 +8271,11 @@
       <c r="F253" t="n">
         <v>623402</v>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -7037,6 +8302,11 @@
       <c r="F254" t="n">
         <v>648791</v>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -7063,6 +8333,11 @@
       <c r="F255" t="n">
         <v>648538</v>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -7089,6 +8364,11 @@
       <c r="F256" t="n">
         <v>622083</v>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -7115,6 +8395,11 @@
       <c r="F257" t="n">
         <v>623605</v>
       </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -7141,6 +8426,11 @@
       <c r="F258" t="n">
         <v>615009</v>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -7167,6 +8457,11 @@
       <c r="F259" t="n">
         <v>671071</v>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -7193,6 +8488,11 @@
       <c r="F260" t="n">
         <v>674256</v>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -7219,6 +8519,11 @@
       <c r="F261" t="n">
         <v>674027</v>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -7245,6 +8550,11 @@
       <c r="F262" t="n">
         <v>622356</v>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -7271,6 +8581,11 @@
       <c r="F263" t="n">
         <v>649575</v>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -7297,6 +8612,11 @@
       <c r="F264" t="n">
         <v>649388</v>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -7323,6 +8643,11 @@
       <c r="F265" t="n">
         <v>649792</v>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -7349,6 +8674,11 @@
       <c r="F266" t="n">
         <v>649423</v>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -7375,6 +8705,11 @@
       <c r="F267" t="n">
         <v>643673</v>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -7401,6 +8736,11 @@
       <c r="F268" t="n">
         <v>675663</v>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -7427,6 +8767,11 @@
       <c r="F269" t="n">
         <v>674314</v>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -7453,6 +8798,11 @@
       <c r="F270" t="n">
         <v>671069</v>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -7479,6 +8829,11 @@
       <c r="F271" t="n">
         <v>641117</v>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -7505,6 +8860,11 @@
       <c r="F272" t="n">
         <v>624795</v>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -7531,6 +8891,11 @@
       <c r="F273" t="n">
         <v>641774</v>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -7557,6 +8922,11 @@
       <c r="F274" t="n">
         <v>675766</v>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -7583,6 +8953,11 @@
       <c r="F275" t="n">
         <v>667399</v>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -7609,6 +8984,11 @@
       <c r="F276" t="n">
         <v>680061</v>
       </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -7635,6 +9015,11 @@
       <c r="F277" t="n">
         <v>668399</v>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -7661,6 +9046,11 @@
       <c r="F278" t="n">
         <v>685497</v>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -7687,6 +9077,11 @@
       <c r="F279" t="n">
         <v>675481</v>
       </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -7713,6 +9108,11 @@
       <c r="F280" t="n">
         <v>682232</v>
       </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -7739,6 +9139,11 @@
       <c r="F281" t="n">
         <v>643596</v>
       </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -7765,6 +9170,11 @@
       <c r="F282" t="n">
         <v>709520</v>
       </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -7791,6 +9201,11 @@
       <c r="F283" t="n">
         <v>667904</v>
       </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -7817,6 +9232,11 @@
       <c r="F284" t="n">
         <v>675386</v>
       </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -7843,6 +9263,11 @@
       <c r="F285" t="n">
         <v>674254</v>
       </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -7869,6 +9294,11 @@
       <c r="F286" t="n">
         <v>674170</v>
       </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -7895,6 +9325,11 @@
       <c r="F287" t="n">
         <v>670902</v>
       </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -7921,6 +9356,11 @@
       <c r="F288" t="n">
         <v>668142</v>
       </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -7947,6 +9387,11 @@
       <c r="F289" t="n">
         <v>675175</v>
       </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -7973,6 +9418,11 @@
       <c r="F290" t="n">
         <v>667834</v>
       </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -7999,6 +9449,11 @@
       <c r="F291" t="n">
         <v>668106</v>
       </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -8025,6 +9480,11 @@
       <c r="F292" t="n">
         <v>672736</v>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -8051,6 +9511,11 @@
       <c r="F293" t="n">
         <v>644319</v>
       </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -8077,6 +9542,11 @@
       <c r="F294" t="n">
         <v>674082</v>
       </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -8103,6 +9573,11 @@
       <c r="F295" t="n">
         <v>675318</v>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -8129,6 +9604,11 @@
       <c r="F296" t="n">
         <v>681841</v>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -8155,6 +9635,11 @@
       <c r="F297" t="n">
         <v>682724</v>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -8181,6 +9666,11 @@
       <c r="F298" t="n">
         <v>647264</v>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -8207,6 +9697,11 @@
       <c r="F299" t="n">
         <v>709856</v>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -8233,6 +9728,11 @@
       <c r="F300" t="n">
         <v>688136</v>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -8259,6 +9759,11 @@
       <c r="F301" t="n">
         <v>641665</v>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -8285,6 +9790,11 @@
       <c r="F302" t="n">
         <v>663156</v>
       </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -8311,6 +9821,11 @@
       <c r="F303" t="n">
         <v>674498</v>
       </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -8337,6 +9852,11 @@
       <c r="F304" t="n">
         <v>674347</v>
       </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -8363,6 +9883,11 @@
       <c r="F305" t="n">
         <v>618350</v>
       </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -8389,6 +9914,11 @@
       <c r="F306" t="n">
         <v>624768</v>
       </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -8415,6 +9945,11 @@
       <c r="F307" t="n">
         <v>668759</v>
       </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -8441,6 +9976,11 @@
       <c r="F308" t="n">
         <v>669593</v>
       </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -8467,6 +10007,11 @@
       <c r="F309" t="n">
         <v>631191</v>
       </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -8493,6 +10038,11 @@
       <c r="F310" t="n">
         <v>623202</v>
       </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -8519,6 +10069,11 @@
       <c r="F311" t="n">
         <v>634944</v>
       </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -8545,6 +10100,11 @@
       <c r="F312" t="n">
         <v>632809</v>
       </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -8571,6 +10131,11 @@
       <c r="F313" t="n">
         <v>622852</v>
       </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -8597,6 +10162,11 @@
       <c r="F314" t="n">
         <v>639692</v>
       </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -8623,6 +10193,11 @@
       <c r="F315" t="n">
         <v>622896</v>
       </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -8649,6 +10224,11 @@
       <c r="F316" t="n">
         <v>677819</v>
       </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -8675,6 +10255,11 @@
       <c r="F317" t="n">
         <v>669165</v>
       </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -8701,6 +10286,11 @@
       <c r="F318" t="n">
         <v>623059</v>
       </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -8727,6 +10317,11 @@
       <c r="F319" t="n">
         <v>647800</v>
       </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -8753,6 +10348,11 @@
       <c r="F320" t="n">
         <v>652237</v>
       </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -8779,6 +10379,11 @@
       <c r="F321" t="n">
         <v>648296</v>
       </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -8805,6 +10410,11 @@
       <c r="F322" t="n">
         <v>644496</v>
       </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -8831,6 +10441,11 @@
       <c r="F323" t="n">
         <v>622929</v>
       </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -8857,6 +10472,11 @@
       <c r="F324" t="n">
         <v>668991</v>
       </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -8883,6 +10503,11 @@
       <c r="F325" t="n">
         <v>681063</v>
       </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -8909,6 +10534,11 @@
       <c r="F326" t="n">
         <v>668055</v>
       </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -8935,6 +10565,11 @@
       <c r="F327" t="n">
         <v>674170</v>
       </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -8961,6 +10596,11 @@
       <c r="F328" t="n">
         <v>675744</v>
       </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -8987,6 +10627,11 @@
       <c r="F329" t="n">
         <v>675519</v>
       </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -9013,6 +10658,11 @@
       <c r="F330" t="n">
         <v>634333</v>
       </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -9039,6 +10689,11 @@
       <c r="F331" t="n">
         <v>682115</v>
       </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -9065,6 +10720,11 @@
       <c r="F332" t="n">
         <v>639813</v>
       </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -9091,6 +10751,11 @@
       <c r="F333" t="n">
         <v>675819</v>
       </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -9117,6 +10782,11 @@
       <c r="F334" t="n">
         <v>648699</v>
       </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -9143,6 +10813,11 @@
       <c r="F335" t="n">
         <v>669656</v>
       </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -9169,6 +10844,11 @@
       <c r="F336" t="n">
         <v>647067</v>
       </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -9195,6 +10875,11 @@
       <c r="F337" t="n">
         <v>668227</v>
       </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -9221,6 +10906,11 @@
       <c r="F338" t="n">
         <v>622811</v>
       </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -9247,6 +10937,11 @@
       <c r="F339" t="n">
         <v>623122</v>
       </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -9273,6 +10968,11 @@
       <c r="F340" t="n">
         <v>648844</v>
       </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -9299,6 +10999,11 @@
       <c r="F341" t="n">
         <v>622415</v>
       </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -9325,6 +11030,11 @@
       <c r="F342" t="n">
         <v>645702</v>
       </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -9351,6 +11061,11 @@
       <c r="F343" t="n">
         <v>633685</v>
       </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -9377,6 +11092,11 @@
       <c r="F344" t="n">
         <v>645673</v>
       </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -9403,6 +11123,11 @@
       <c r="F345" t="n">
         <v>599166</v>
       </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -9429,6 +11154,11 @@
       <c r="F346" t="n">
         <v>669268</v>
       </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -9455,6 +11185,11 @@
       <c r="F347" t="n">
         <v>623180</v>
       </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -9481,6 +11216,11 @@
       <c r="F348" t="n">
         <v>617806</v>
       </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -9507,6 +11247,11 @@
       <c r="F349" t="n">
         <v>649399</v>
       </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -9533,6 +11278,11 @@
       <c r="F350" t="n">
         <v>648396</v>
       </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -9559,6 +11309,11 @@
       <c r="F351" t="n">
         <v>679109</v>
       </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -9585,6 +11340,11 @@
       <c r="F352" t="n">
         <v>641655</v>
       </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -9611,6 +11371,11 @@
       <c r="F353" t="n">
         <v>648636</v>
       </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -9637,6 +11402,11 @@
       <c r="F354" t="n">
         <v>634365</v>
       </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -9663,6 +11433,11 @@
       <c r="F355" t="n">
         <v>648675</v>
       </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -9689,6 +11464,11 @@
       <c r="F356" t="n">
         <v>614336</v>
       </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -9715,6 +11495,11 @@
       <c r="F357" t="n">
         <v>649881</v>
       </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -9741,6 +11526,11 @@
       <c r="F358" t="n">
         <v>648815</v>
       </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -9767,6 +11557,11 @@
       <c r="F359" t="n">
         <v>622145</v>
       </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -9793,6 +11588,11 @@
       <c r="F360" t="n">
         <v>623111</v>
       </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -9819,6 +11619,11 @@
       <c r="F361" t="n">
         <v>622703</v>
       </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -9845,6 +11650,11 @@
       <c r="F362" t="n">
         <v>664110</v>
       </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -9871,6 +11681,11 @@
       <c r="F363" t="n">
         <v>669962</v>
       </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -9897,6 +11712,11 @@
       <c r="F364" t="n">
         <v>677819</v>
       </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -9923,6 +11743,11 @@
       <c r="F365" t="n">
         <v>677819</v>
       </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -9949,6 +11774,11 @@
       <c r="F366" t="n">
         <v>683254</v>
       </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -9975,6 +11805,11 @@
       <c r="F367" t="n">
         <v>669165</v>
       </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -10001,6 +11836,11 @@
       <c r="F368" t="n">
         <v>665584</v>
       </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -10027,6 +11867,11 @@
       <c r="F369" t="n">
         <v>664110</v>
       </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -10053,6 +11898,11 @@
       <c r="F370" t="n">
         <v>669047</v>
       </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -10079,6 +11929,11 @@
       <c r="F371" t="n">
         <v>681978</v>
       </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -10105,6 +11960,11 @@
       <c r="F372" t="n">
         <v>664117</v>
       </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -10131,6 +11991,11 @@
       <c r="F373" t="n">
         <v>677666</v>
       </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -10157,6 +12022,11 @@
       <c r="F374" t="n">
         <v>677962</v>
       </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -10183,6 +12053,11 @@
       <c r="F375" t="n">
         <v>669324</v>
       </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -10209,6 +12084,11 @@
       <c r="F376" t="n">
         <v>665533</v>
       </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -10235,6 +12115,11 @@
       <c r="F377" t="n">
         <v>648936</v>
       </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -10261,6 +12146,11 @@
       <c r="F378" t="n">
         <v>623202</v>
       </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -10287,6 +12177,11 @@
       <c r="F379" t="n">
         <v>623387</v>
       </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -10313,6 +12208,11 @@
       <c r="F380" t="n">
         <v>622111</v>
       </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -10339,6 +12239,11 @@
       <c r="F381" t="n">
         <v>649566</v>
       </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -10365,6 +12270,11 @@
       <c r="F382" t="n">
         <v>641145</v>
       </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -10391,6 +12301,11 @@
       <c r="F383" t="n">
         <v>649651</v>
       </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -10417,6 +12332,11 @@
       <c r="F384" t="n">
         <v>648321</v>
       </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -10443,6 +12363,11 @@
       <c r="F385" t="n">
         <v>620335</v>
       </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -10469,6 +12394,11 @@
       <c r="F386" t="n">
         <v>618429</v>
       </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -10495,6 +12425,11 @@
       <c r="F387" t="n">
         <v>622735</v>
       </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -10521,6 +12456,11 @@
       <c r="F388" t="n">
         <v>637205</v>
       </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -10547,6 +12487,11 @@
       <c r="F389" t="n">
         <v>616985</v>
       </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -10573,6 +12518,11 @@
       <c r="F390" t="n">
         <v>623463</v>
       </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -10599,6 +12549,11 @@
       <c r="F391" t="n">
         <v>623552</v>
       </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -10625,6 +12580,11 @@
       <c r="F392" t="n">
         <v>649172</v>
       </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -10651,6 +12611,11 @@
       <c r="F393" t="n">
         <v>623463</v>
       </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -10677,6 +12642,11 @@
       <c r="F394" t="n">
         <v>622082</v>
       </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -10703,6 +12673,11 @@
       <c r="F395" t="n">
         <v>657370</v>
       </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -10729,6 +12704,11 @@
       <c r="F396" t="n">
         <v>668049</v>
       </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -10755,6 +12735,11 @@
       <c r="F397" t="n">
         <v>645796</v>
       </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -10781,6 +12766,11 @@
       <c r="F398" t="n">
         <v>642788</v>
       </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -10807,6 +12797,11 @@
       <c r="F399" t="n">
         <v>622578</v>
       </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -10833,6 +12828,11 @@
       <c r="F400" t="n">
         <v>623543</v>
       </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -10859,6 +12859,11 @@
       <c r="F401" t="n">
         <v>648029</v>
       </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -10885,6 +12890,11 @@
       <c r="F402" t="n">
         <v>618386</v>
       </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -10911,6 +12921,11 @@
       <c r="F403" t="n">
         <v>628605</v>
       </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -10937,6 +12952,11 @@
       <c r="F404" t="n">
         <v>649172</v>
       </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -10963,6 +12983,11 @@
       <c r="F405" t="n">
         <v>622106</v>
       </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -10989,6 +13014,11 @@
       <c r="F406" t="n">
         <v>623599</v>
       </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -11015,6 +13045,11 @@
       <c r="F407" t="n">
         <v>644902</v>
       </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -11041,6 +13076,11 @@
       <c r="F408" t="n">
         <v>588352</v>
       </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -11067,6 +13107,11 @@
       <c r="F409" t="n">
         <v>618642</v>
       </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -11093,6 +13138,11 @@
       <c r="F410" t="n">
         <v>641079</v>
       </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -11119,6 +13169,11 @@
       <c r="F411" t="n">
         <v>636386</v>
       </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -11145,6 +13200,11 @@
       <c r="F412" t="n">
         <v>639451</v>
       </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -11171,6 +13231,11 @@
       <c r="F413" t="n">
         <v>589097</v>
       </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -11197,6 +13262,11 @@
       <c r="F414" t="n">
         <v>593878</v>
       </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -11223,6 +13293,11 @@
       <c r="F415" t="n">
         <v>617632</v>
       </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -11249,6 +13324,11 @@
       <c r="F416" t="n">
         <v>620335</v>
       </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -11275,6 +13355,11 @@
       <c r="F417" t="n">
         <v>664522</v>
       </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -11301,6 +13386,11 @@
       <c r="F418" t="n">
         <v>647345</v>
       </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -11327,6 +13417,11 @@
       <c r="F419" t="n">
         <v>674937</v>
       </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -11353,6 +13448,11 @@
       <c r="F420" t="n">
         <v>644860</v>
       </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -11379,6 +13479,11 @@
       <c r="F421" t="n">
         <v>651894</v>
       </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -11405,6 +13510,11 @@
       <c r="F422" t="n">
         <v>643055</v>
       </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -11431,6 +13541,11 @@
       <c r="F423" t="n">
         <v>621030</v>
       </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -11457,6 +13572,11 @@
       <c r="F424" t="n">
         <v>658515</v>
       </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -11483,6 +13603,11 @@
       <c r="F425" t="n">
         <v>640423</v>
       </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -11509,6 +13634,11 @@
       <c r="F426" t="n">
         <v>631380</v>
       </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -11535,6 +13665,11 @@
       <c r="F427" t="n">
         <v>626316</v>
       </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -11561,6 +13696,11 @@
       <c r="F428" t="n">
         <v>640995</v>
       </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -11587,6 +13727,11 @@
       <c r="F429" t="n">
         <v>635767</v>
       </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -11613,6 +13758,11 @@
       <c r="F430" t="n">
         <v>661359</v>
       </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -11639,6 +13789,11 @@
       <c r="F431" t="n">
         <v>631463</v>
       </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -11665,6 +13820,11 @@
       <c r="F432" t="n">
         <v>623173</v>
       </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -11691,6 +13851,11 @@
       <c r="F433" t="n">
         <v>644992</v>
       </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -11717,6 +13882,11 @@
       <c r="F434" t="n">
         <v>622073</v>
       </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -11743,6 +13913,11 @@
       <c r="F435" t="n">
         <v>600223</v>
       </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -11769,6 +13944,11 @@
       <c r="F436" t="n">
         <v>604190</v>
       </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -11795,6 +13975,11 @@
       <c r="F437" t="n">
         <v>675027</v>
       </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -11821,6 +14006,11 @@
       <c r="F438" t="n">
         <v>622584</v>
       </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -11847,6 +14037,11 @@
       <c r="F439" t="n">
         <v>593978</v>
       </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -11873,6 +14068,11 @@
       <c r="F440" t="n">
         <v>625183</v>
       </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -11899,6 +14099,11 @@
       <c r="F441" t="n">
         <v>662040</v>
       </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -11925,6 +14130,11 @@
       <c r="F442" t="n">
         <v>664668</v>
       </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -11951,6 +14161,11 @@
       <c r="F443" t="n">
         <v>648099</v>
       </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -11977,6 +14192,11 @@
       <c r="F444" t="n">
         <v>622718</v>
       </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -12003,6 +14223,11 @@
       <c r="F445" t="n">
         <v>648727</v>
       </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -12029,6 +14254,11 @@
       <c r="F446" t="n">
         <v>622514</v>
       </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -12055,6 +14285,11 @@
       <c r="F447" t="n">
         <v>623904</v>
       </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -12081,6 +14316,11 @@
       <c r="F448" t="n">
         <v>651188</v>
       </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -12107,6 +14347,11 @@
       <c r="F449" t="n">
         <v>649381</v>
       </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -12133,6 +14378,11 @@
       <c r="F450" t="n">
         <v>662271</v>
       </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -12159,6 +14409,11 @@
       <c r="F451" t="n">
         <v>641001</v>
       </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -12185,6 +14440,11 @@
       <c r="F452" t="n">
         <v>589015</v>
       </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -12211,6 +14471,11 @@
       <c r="F453" t="n">
         <v>645305</v>
       </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -12237,6 +14502,11 @@
       <c r="F454" t="n">
         <v>622464</v>
       </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -12263,6 +14533,11 @@
       <c r="F455" t="n">
         <v>622104</v>
       </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -12289,6 +14564,11 @@
       <c r="F456" t="n">
         <v>648332</v>
       </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -12315,6 +14595,11 @@
       <c r="F457" t="n">
         <v>678674</v>
       </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -12341,6 +14626,11 @@
       <c r="F458" t="n">
         <v>649726</v>
       </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -12367,6 +14657,11 @@
       <c r="F459" t="n">
         <v>585645</v>
       </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -12393,6 +14688,11 @@
       <c r="F460" t="n">
         <v>623394</v>
       </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -12419,6 +14719,11 @@
       <c r="F461" t="n">
         <v>623757</v>
       </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -12445,6 +14750,11 @@
       <c r="F462" t="n">
         <v>696747</v>
       </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -12471,6 +14781,11 @@
       <c r="F463" t="n">
         <v>664154</v>
       </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -12497,6 +14812,11 @@
       <c r="F464" t="n">
         <v>648647</v>
       </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -12523,6 +14843,11 @@
       <c r="F465" t="n">
         <v>651857</v>
       </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -12549,6 +14874,11 @@
       <c r="F466" t="n">
         <v>623008</v>
       </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -12575,6 +14905,11 @@
       <c r="F467" t="n">
         <v>622390</v>
       </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -12601,6 +14936,11 @@
       <c r="F468" t="n">
         <v>634833</v>
       </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -12627,6 +14967,11 @@
       <c r="F469" t="n">
         <v>647990</v>
       </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -12653,6 +14998,11 @@
       <c r="F470" t="n">
         <v>648925</v>
       </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -12679,6 +15029,11 @@
       <c r="F471" t="n">
         <v>647688</v>
       </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -12705,6 +15060,11 @@
       <c r="F472" t="n">
         <v>648993</v>
       </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -12731,6 +15091,11 @@
       <c r="F473" t="n">
         <v>650114</v>
       </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -12757,6 +15122,11 @@
       <c r="F474" t="n">
         <v>622236</v>
       </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -12783,6 +15153,11 @@
       <c r="F475" t="n">
         <v>623249</v>
       </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -12809,6 +15184,11 @@
       <c r="F476" t="n">
         <v>622811</v>
       </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -12835,6 +15215,11 @@
       <c r="F477" t="n">
         <v>647990</v>
       </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -12861,6 +15246,11 @@
       <c r="F478" t="n">
         <v>648540</v>
       </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -12887,6 +15277,11 @@
       <c r="F479" t="n">
         <v>647393</v>
       </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -12913,6 +15308,11 @@
       <c r="F480" t="n">
         <v>648192</v>
       </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -12939,6 +15339,11 @@
       <c r="F481" t="n">
         <v>641168</v>
       </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -12965,6 +15370,11 @@
       <c r="F482" t="n">
         <v>622371</v>
       </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -12991,6 +15401,11 @@
       <c r="F483" t="n">
         <v>623534</v>
       </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -13017,6 +15432,11 @@
       <c r="F484" t="n">
         <v>648540</v>
       </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -13043,6 +15463,11 @@
       <c r="F485" t="n">
         <v>620433</v>
       </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -13069,6 +15494,11 @@
       <c r="F486" t="n">
         <v>623904</v>
       </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -13095,6 +15525,11 @@
       <c r="F487" t="n">
         <v>653496</v>
       </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -13121,6 +15556,11 @@
       <c r="F488" t="n">
         <v>643015</v>
       </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -13147,6 +15587,11 @@
       <c r="F489" t="n">
         <v>647967</v>
       </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -13173,6 +15618,11 @@
       <c r="F490" t="n">
         <v>623151</v>
       </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -13199,6 +15649,11 @@
       <c r="F491" t="n">
         <v>588884</v>
       </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -13225,6 +15680,11 @@
       <c r="F492" t="n">
         <v>641145</v>
       </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -13251,6 +15711,11 @@
       <c r="F493" t="n">
         <v>623113</v>
       </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -13277,6 +15742,11 @@
       <c r="F494" t="n">
         <v>649510</v>
       </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -13303,6 +15773,11 @@
       <c r="F495" t="n">
         <v>647990</v>
       </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -13329,6 +15804,11 @@
       <c r="F496" t="n">
         <v>662336</v>
       </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -13355,6 +15835,11 @@
       <c r="F497" t="n">
         <v>649388</v>
       </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -13381,6 +15866,11 @@
       <c r="F498" t="n">
         <v>623151</v>
       </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -13407,6 +15897,11 @@
       <c r="F499" t="n">
         <v>623418</v>
       </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -13433,6 +15928,11 @@
       <c r="F500" t="n">
         <v>622402</v>
       </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -13459,6 +15959,11 @@
       <c r="F501" t="n">
         <v>649501</v>
       </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -13485,6 +15990,11 @@
       <c r="F502" t="n">
         <v>648540</v>
       </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -13511,6 +16021,11 @@
       <c r="F503" t="n">
         <v>642676</v>
       </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -13537,6 +16052,11 @@
       <c r="F504" t="n">
         <v>648748</v>
       </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -13563,6 +16083,11 @@
       <c r="F505" t="n">
         <v>623003</v>
       </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -13589,6 +16114,11 @@
       <c r="F506" t="n">
         <v>622851</v>
       </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -13615,6 +16145,11 @@
       <c r="F507" t="n">
         <v>667907</v>
       </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -13641,6 +16176,11 @@
       <c r="F508" t="n">
         <v>605691</v>
       </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -13667,6 +16207,11 @@
       <c r="F509" t="n">
         <v>649066</v>
       </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -13693,6 +16238,11 @@
       <c r="F510" t="n">
         <v>620718</v>
       </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -13719,6 +16269,11 @@
       <c r="F511" t="n">
         <v>622441</v>
       </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -13745,6 +16300,11 @@
       <c r="F512" t="n">
         <v>623058</v>
       </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -13771,6 +16331,11 @@
       <c r="F513" t="n">
         <v>618914</v>
       </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -13797,6 +16362,11 @@
       <c r="F514" t="n">
         <v>623474</v>
       </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -13823,6 +16393,11 @@
       <c r="F515" t="n">
         <v>647676</v>
       </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -13849,6 +16424,11 @@
       <c r="F516" t="n">
         <v>648099</v>
       </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -13875,6 +16455,11 @@
       <c r="F517" t="n">
         <v>641873</v>
       </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -13901,6 +16486,11 @@
       <c r="F518" t="n">
         <v>622696</v>
       </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -13927,6 +16517,11 @@
       <c r="F519" t="n">
         <v>630138</v>
       </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -13952,6 +16547,11 @@
       </c>
       <c r="F520" t="n">
         <v>631380</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>moe_mosdot_coordinates</t>
+        </is>
       </c>
     </row>
   </sheetData>
